--- a/artfynd/A 19948-2025 artfynd.xlsx
+++ b/artfynd/A 19948-2025 artfynd.xlsx
@@ -882,7 +882,7 @@
         <v>126348508</v>
       </c>
       <c r="B4" t="n">
-        <v>97233</v>
+        <v>97236</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 19948-2025 artfynd.xlsx
+++ b/artfynd/A 19948-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126348493</v>
       </c>
       <c r="B2" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>126348496</v>
       </c>
       <c r="B3" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>126348508</v>
       </c>
       <c r="B4" t="n">
-        <v>97236</v>
+        <v>97245</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
         <v>126348494</v>
       </c>
       <c r="B5" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 19948-2025 artfynd.xlsx
+++ b/artfynd/A 19948-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,48 +675,52 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126348493</v>
+        <v>127743703</v>
       </c>
       <c r="B2" t="n">
-        <v>57657</v>
+        <v>92083</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>1503</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(P.Karst.) Miettinen</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Digerberget, Hjd</t>
+          <t>Putten, Hjd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>412166</v>
+        <v>411997</v>
       </c>
       <c r="R2" t="n">
-        <v>6966378</v>
+        <v>6966423</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -740,17 +744,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-06-30</t>
+          <t>2025-07-06</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-06-30</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
+          <t>2025-07-06</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -765,22 +774,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Amanda Selinder</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Amanda Selinder</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126348496</v>
+        <v>127743697</v>
       </c>
       <c r="B3" t="n">
-        <v>57657</v>
+        <v>79413</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -788,37 +797,41 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6450</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Ach.) Parrique</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Digerberget, Hjd</t>
+          <t>Putten, Hjd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>412108</v>
+        <v>411956</v>
       </c>
       <c r="R3" t="n">
-        <v>6966128</v>
+        <v>6966544</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -842,17 +855,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-06-30</t>
+          <t>2025-07-06</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-06-30</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
+          <t>2025-07-06</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -867,44 +885,44 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Amanda Selinder</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Amanda Selinder</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126348508</v>
+        <v>126348493</v>
       </c>
       <c r="B4" t="n">
-        <v>97245</v>
+        <v>57953</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221941</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -914,10 +932,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>411930</v>
+        <v>412166</v>
       </c>
       <c r="R4" t="n">
-        <v>6966300</v>
+        <v>6966378</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -950,6 +968,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -979,7 +1002,7 @@
         <v>126348494</v>
       </c>
       <c r="B5" t="n">
-        <v>57657</v>
+        <v>57953</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1075,6 +1098,205 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>126348496</v>
+      </c>
+      <c r="B6" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Digerberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>412108</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6966128</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>126348508</v>
+      </c>
+      <c r="B7" t="n">
+        <v>97989</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>221941</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Digerberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>411930</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6966300</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 19948-2025 artfynd.xlsx
+++ b/artfynd/A 19948-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -783,6 +788,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127743703</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -894,6 +904,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127743697</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -996,6 +1011,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126348493</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1098,6 +1118,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126348494</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1200,6 +1225,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126348496</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1297,8 +1327,21 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126348508</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>